--- a/examples/validation_results/validation_truss_temperature.xlsx
+++ b/examples/validation_results/validation_truss_temperature.xlsx
@@ -1135,17 +1135,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fx ()</t>
+          <t>Fx (KN)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Fy ()</t>
+          <t>Fy (KN)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fz ()</t>
+          <t>Fz (KN)</t>
         </is>
       </c>
     </row>
